--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -1122,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>96045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R6" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,45 +1229,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>96045</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R7" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>8436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R4" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>4778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R5" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1122,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>96046</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R6" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,54 +1238,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>96046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R7" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>4778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B5" t="n">
-        <v>4778</v>
+        <v>8436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R5" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127144083</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>8439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R4" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R5" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>96050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R6" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,45 +1229,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>96046</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R7" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127144431</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R5" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R4" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R5" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
         <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127144431</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R5" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1122,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>96052</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R6" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,54 +1238,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>96052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R7" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -1122,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>96052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R6" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,45 +1229,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>96052</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R7" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144445</v>
       </c>
       <c r="B6" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127144421</v>
       </c>
       <c r="B7" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127144431</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R4" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R5" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1122,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144445</v>
+        <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>96061</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616500</v>
+        <v>616478</v>
       </c>
       <c r="R6" t="n">
-        <v>6539826</v>
+        <v>6539763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,54 +1238,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144421</v>
+        <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>91361</v>
+        <v>96069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616478</v>
+        <v>616500</v>
       </c>
       <c r="R7" t="n">
-        <v>6539763</v>
+        <v>6539826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127144431</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143643</v>
+        <v>127143593</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617087</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6539495</v>
+        <v>6539536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143593</v>
+        <v>127143643</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617234</v>
+        <v>617087</v>
       </c>
       <c r="R5" t="n">
-        <v>6539536</v>
+        <v>6539495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
         <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127144083</v>
       </c>
       <c r="B2" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127143688</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127143593</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>4778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>127143643</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>127144421</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>127144445</v>
       </c>
       <c r="B7" t="n">
-        <v>96070</v>
+        <v>96039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127144499</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>91339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127144531</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127144431</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127144083</v>
+        <v>127144445</v>
       </c>
       <c r="B2" t="n">
-        <v>8439</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Solberga, Solberga, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616703</v>
+        <v>616500</v>
       </c>
       <c r="R2" t="n">
-        <v>6539698</v>
+        <v>6539826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127143688</v>
+        <v>127144859</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617052</v>
+        <v>617016</v>
       </c>
       <c r="R3" t="n">
-        <v>6539565</v>
+        <v>6539502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127143593</v>
+        <v>127143688</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617052</v>
       </c>
       <c r="R4" t="n">
-        <v>6539536</v>
+        <v>6539565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,50 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127143643</v>
+        <v>127144421</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Paris, Paris, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617087</v>
+        <v>616478</v>
       </c>
       <c r="R5" t="n">
-        <v>6539495</v>
+        <v>6539763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127144421</v>
+        <v>127144499</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,26 +1149,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616478</v>
+        <v>616548</v>
       </c>
       <c r="R6" t="n">
-        <v>6539763</v>
+        <v>6539798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,45 +1228,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127144445</v>
+        <v>127144531</v>
       </c>
       <c r="B7" t="n">
-        <v>96070</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Srm</t>
+          <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616500</v>
+        <v>616564</v>
       </c>
       <c r="R7" t="n">
-        <v>6539826</v>
+        <v>6539746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,45 +1344,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127144499</v>
+        <v>127144431</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Parisabergen, Parisabergen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616548</v>
+        <v>616484</v>
       </c>
       <c r="R8" t="n">
-        <v>6539798</v>
+        <v>6539778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,54 +1456,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127144531</v>
+        <v>127143723</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616564</v>
+        <v>617039</v>
       </c>
       <c r="R9" t="n">
-        <v>6539746</v>
+        <v>6539575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,50 +1568,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127144431</v>
+        <v>127143593</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>4781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Parisabergen, Parisabergen, Srm</t>
+          <t>Paris, Paris, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616484</v>
+        <v>617234</v>
       </c>
       <c r="R10" t="n">
-        <v>6539778</v>
+        <v>6539536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,6 +1672,230 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127143643</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Paris, Paris, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>617087</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6539495</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ripsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127144083</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Parisabergen, Parisabergen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616703</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ripsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36547-2025 artfynd.xlsx
+++ b/artfynd/A 36547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127143688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144421</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144499</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144531</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127143723</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127143593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127143643</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,8 +1951,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127144083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>